--- a/data/excel/FlightManualBooking.xlsx
+++ b/data/excel/FlightManualBooking.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEC6407-DD7B-43F9-8FE7-4AB64D3EDD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6DDCA4-28C7-4557-90AD-7D44FC2F0BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BODC" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
-    <sheet name="BOCA" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="BOCA" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="232">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -559,9 +561,6 @@
     <t>7000777107,8800888824,8800888825,8800888826,8800888827</t>
   </si>
   <si>
-    <t>777000504,8888000824,8888888825,8888888826,8888888827</t>
-  </si>
-  <si>
     <t>F1CD@9E4B</t>
   </si>
   <si>
@@ -574,16 +573,166 @@
     <t>Verify manual booking for one way flight with 1 adult , 1 child</t>
   </si>
   <si>
+    <t>7777000116,8888008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>7077771007,7077771009,7777771010,7777771008,7777771009</t>
+  </si>
+  <si>
+    <t>k.gaurav</t>
+  </si>
+  <si>
+    <t>07DE6@EAB</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>777000510,8888000824,8888888825,8888888826,8888888827</t>
+  </si>
+  <si>
+    <t>6E</t>
+  </si>
+  <si>
+    <t>6E-Indigo</t>
+  </si>
+  <si>
+    <t>E0@DA44FE</t>
+  </si>
+  <si>
+    <t>Saurav Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Nachin Shah,Sunita Shah</t>
+  </si>
+  <si>
+    <t>Aaurav Shah,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Saurav Shah,Munit Shah</t>
+  </si>
+  <si>
+    <t>Rachin Shah,Sunita Shah</t>
+  </si>
+  <si>
+    <t>Sunil Shah,Sunita Shah</t>
+  </si>
+  <si>
     <t>5-Aug-2024,5-Feb-2023</t>
   </si>
   <si>
-    <t>7777777112,7777777113,7777777114,8888888826,8888888827</t>
-  </si>
-  <si>
-    <t>7777000116,8888008117,8888888118,8888888828,8888888829</t>
-  </si>
-  <si>
-    <t>7077771007,7077771009,7777771010,7777771008,7777771009</t>
+    <t>8-Aug-2025</t>
+  </si>
+  <si>
+    <t>10-Aug-2025</t>
+  </si>
+  <si>
+    <t>11-Aug-2025</t>
+  </si>
+  <si>
+    <t>12-Aug-2025</t>
+  </si>
+  <si>
+    <t>13-Aug-2025</t>
+  </si>
+  <si>
+    <t>14-Aug-2025</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>CCU</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with domestic search</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with 1 adult with internation search</t>
+  </si>
+  <si>
+    <t>DXB</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight internation search with VAT</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with miscellaneous charges</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with 1 adult with GDS supplier</t>
+  </si>
+  <si>
+    <t>Prince Singh,Sumit Shah</t>
+  </si>
+  <si>
+    <t>Q124506</t>
+  </si>
+  <si>
+    <t>260520251,8888008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with adult with taxes</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with multi passenger</t>
+  </si>
+  <si>
+    <t>Verify manual booking for one way flight with 1 adult, 1 child with misc charges</t>
+  </si>
+  <si>
+    <t>240520250,8888008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>240520251,8888008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>240520252,250520253,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>240520254,250520255,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>240520256,8888008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>240520257,8888008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>24520257,2488008117,8888888118,8888888828,8888888829</t>
+  </si>
+  <si>
+    <t>24520257,2488008117,2488888118,8888888828,8888888829</t>
   </si>
 </sst>
 </file>
@@ -678,7 +827,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -699,6 +848,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3369,8 +3524,2399 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BBB5E8-228E-4947-B83F-9EA861DA2AAA}">
+  <dimension ref="A1:BP9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="21" max="21" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BC1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="BD1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="BE1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="BG1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="BH1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="BI1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BJ1" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK1" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL1" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="BO1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2">
+        <v>1245011</v>
+      </c>
+      <c r="T2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2">
+        <v>130</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB2">
+        <v>12</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE2">
+        <v>784552</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI2">
+        <v>141</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK2">
+        <v>12</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM2">
+        <v>14</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP2">
+        <v>784523</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR2">
+        <v>110</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX2">
+        <v>30</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA2">
+        <v>2</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD2">
+        <v>40</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG2">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK2" s="9">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN2">
+        <v>30</v>
+      </c>
+      <c r="BO2" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I3" s="9">
+        <v>1</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="M3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" t="s">
+        <v>201</v>
+      </c>
+      <c r="S3">
+        <v>1245012</v>
+      </c>
+      <c r="T3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" t="s">
+        <v>26</v>
+      </c>
+      <c r="X3">
+        <v>132</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z3">
+        <v>6</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB3">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>784554</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI3">
+        <v>143</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK3">
+        <v>14</v>
+      </c>
+      <c r="AL3" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM3">
+        <v>16</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP3">
+        <v>784525</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR3">
+        <v>112</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU3">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX3">
+        <v>31</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA3">
+        <v>2</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD3">
+        <v>41</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG3">
+        <v>2</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK3" s="9">
+        <v>3</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN3">
+        <v>30</v>
+      </c>
+      <c r="BO3" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="M4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" t="s">
+        <v>214</v>
+      </c>
+      <c r="S4">
+        <v>1245013</v>
+      </c>
+      <c r="T4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4">
+        <v>134</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z4">
+        <v>8</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="AB4">
+        <v>16</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>784556</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI4">
+        <v>145</v>
+      </c>
+      <c r="AJ4" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK4">
+        <v>16</v>
+      </c>
+      <c r="AL4" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM4">
+        <v>18</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP4">
+        <v>784527</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR4">
+        <v>114</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU4">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX4">
+        <v>32</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA4">
+        <v>2</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD4">
+        <v>42</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG4">
+        <v>2</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK4" s="9">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN4">
+        <v>30</v>
+      </c>
+      <c r="BO4" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" t="s">
+        <v>200</v>
+      </c>
+      <c r="S5">
+        <v>1245014</v>
+      </c>
+      <c r="T5" t="s">
+        <v>26</v>
+      </c>
+      <c r="U5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" t="s">
+        <v>36</v>
+      </c>
+      <c r="W5" t="s">
+        <v>26</v>
+      </c>
+      <c r="X5">
+        <v>131</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z5">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB5">
+        <v>13</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>204</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE5">
+        <v>784553</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5">
+        <v>142</v>
+      </c>
+      <c r="AJ5" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK5">
+        <v>13</v>
+      </c>
+      <c r="AL5" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM5">
+        <v>15</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>205</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP5">
+        <v>784524</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR5">
+        <v>111</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX5">
+        <v>33</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA5">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD5">
+        <v>43</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG5">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK5" s="9">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN5">
+        <v>30</v>
+      </c>
+      <c r="BO5" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N6" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>13</v>
+      </c>
+      <c r="R6" t="s">
+        <v>202</v>
+      </c>
+      <c r="S6">
+        <v>1245015</v>
+      </c>
+      <c r="T6" t="s">
+        <v>26</v>
+      </c>
+      <c r="U6" t="s">
+        <v>25</v>
+      </c>
+      <c r="V6" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" t="s">
+        <v>26</v>
+      </c>
+      <c r="X6">
+        <v>133</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z6">
+        <v>7</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB6">
+        <v>15</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE6">
+        <v>784555</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI6">
+        <v>144</v>
+      </c>
+      <c r="AJ6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK6">
+        <v>15</v>
+      </c>
+      <c r="AL6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM6">
+        <v>17</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP6">
+        <v>784526</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR6">
+        <v>113</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>182</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX6">
+        <v>34</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA6">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD6">
+        <v>44</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG6">
+        <v>2</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK6" s="9">
+        <v>2</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN6">
+        <v>30</v>
+      </c>
+      <c r="BO6" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M7" t="s">
+        <v>191</v>
+      </c>
+      <c r="N7" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>14</v>
+      </c>
+      <c r="R7" t="s">
+        <v>203</v>
+      </c>
+      <c r="S7">
+        <v>1245016</v>
+      </c>
+      <c r="T7" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" t="s">
+        <v>25</v>
+      </c>
+      <c r="V7" t="s">
+        <v>36</v>
+      </c>
+      <c r="W7" t="s">
+        <v>26</v>
+      </c>
+      <c r="X7">
+        <v>135</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z7">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB7">
+        <v>17</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE7">
+        <v>784557</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI7">
+        <v>146</v>
+      </c>
+      <c r="AJ7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK7">
+        <v>17</v>
+      </c>
+      <c r="AL7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM7">
+        <v>19</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>209</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP7">
+        <v>784528</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR7">
+        <v>115</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>182</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX7">
+        <v>35</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA7">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD7">
+        <v>45</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG7">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK7" s="9">
+        <v>3</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN7">
+        <v>30</v>
+      </c>
+      <c r="BO7" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9">
+        <v>1</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="M8" t="s">
+        <v>192</v>
+      </c>
+      <c r="N8" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" t="s">
+        <v>200</v>
+      </c>
+      <c r="S8">
+        <v>1245017</v>
+      </c>
+      <c r="T8" t="s">
+        <v>26</v>
+      </c>
+      <c r="U8" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W8" t="s">
+        <v>26</v>
+      </c>
+      <c r="X8">
+        <v>136</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z8">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="AB8">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE8">
+        <v>784558</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI8">
+        <v>147</v>
+      </c>
+      <c r="AJ8" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK8">
+        <v>18</v>
+      </c>
+      <c r="AL8" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM8">
+        <v>20</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>208</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP8">
+        <v>784529</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR8">
+        <v>116</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>182</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU8">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX8">
+        <v>36</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA8">
+        <v>2</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD8">
+        <v>46</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG8">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK8" s="9">
+        <v>2</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN8">
+        <v>30</v>
+      </c>
+      <c r="BO8" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R9" t="s">
+        <v>201</v>
+      </c>
+      <c r="S9">
+        <v>1245018</v>
+      </c>
+      <c r="T9" t="s">
+        <v>26</v>
+      </c>
+      <c r="U9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" t="s">
+        <v>26</v>
+      </c>
+      <c r="X9">
+        <v>137</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z9">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB9">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE9">
+        <v>784559</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI9">
+        <v>148</v>
+      </c>
+      <c r="AJ9" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK9">
+        <v>19</v>
+      </c>
+      <c r="AL9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM9">
+        <v>21</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>211</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP9">
+        <v>784530</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR9">
+        <v>117</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX9">
+        <v>37</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA9">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD9">
+        <v>47</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG9">
+        <v>2</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK9" s="9">
+        <v>3</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN9">
+        <v>30</v>
+      </c>
+      <c r="BO9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F9" xr:uid="{A29B4A08-05CA-4008-A849-27AFD8FFBF1D}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D9" xr:uid="{BBAE286E-B6D3-4218-976F-A71F01ED78FF}">
+      <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E9" xr:uid="{3EC4F13E-BCCA-4772-8647-53AA1D1B65F6}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK9" xr:uid="{BCC8B231-13B7-47A7-BDCA-C66A282FD72A}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V9" xr:uid="{034290E4-D1FD-4F16-9DD5-5437924D57B0}">
+      <formula1>"One Way,Round Trip"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP2:BP9" xr:uid="{8DB4C3C3-0A7B-4897-B5CF-BB2EE1C28CD2}">
+      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG9 BA2:BA9 AU2:AU9" xr:uid="{EEF66A42-53F1-4058-A16B-C0487DD48219}">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ2:BJ9 BE2:BE9 AY2:AY9 AS2:AS9" xr:uid="{0E4E7E23-D380-46C3-BD8C-4B0748B82828}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2:AQ9" xr:uid="{18DA5828-2199-41F6-8427-C741EF6296BC}">
+      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K9" xr:uid="{01E79EBE-9DB8-4D4E-A221-C34AE5F61A94}">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G9" xr:uid="{72CDA842-E5F3-463E-97C8-7E5A8ACBB057}">
+      <formula1>"E0@DA44FE,Ankur@721,Piyush@12345"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H9" xr:uid="{8D86E4AA-E1E7-478A-BBA2-9491538EDDF3}">
+      <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{10A7EFD1-BE5D-4396-A760-84BF23123860}"/>
+    <hyperlink ref="G2" r:id="rId2" display="EE6B4B@E7" xr:uid="{6719B0C9-5950-44B0-9A27-EA6B8286DCA2}"/>
+    <hyperlink ref="H5" r:id="rId3" display="ankit@quadlabs.com" xr:uid="{2231D8C5-F44D-440A-B7C5-A4FAD9EF0C03}"/>
+    <hyperlink ref="H3" r:id="rId4" display="ankit@quadlabs.com" xr:uid="{51C6FC53-1230-4A1C-B6B1-B58A16ACD4D0}"/>
+    <hyperlink ref="H6" r:id="rId5" display="ankit@quadlabs.com" xr:uid="{AD2586D5-A9B7-4493-A971-EC415EA140E1}"/>
+    <hyperlink ref="H4" r:id="rId6" display="ankit@quadlabs.com" xr:uid="{A579F0B2-F78C-4720-9955-DFD9C418C1CE}"/>
+    <hyperlink ref="H7" r:id="rId7" display="ankit@quadlabs.com" xr:uid="{FB796EA8-1082-4578-94A3-EB5C5AB4A6CD}"/>
+    <hyperlink ref="H8" r:id="rId8" display="ankit@quadlabs.com" xr:uid="{B1D13C82-D817-4F25-BE29-70D937542294}"/>
+    <hyperlink ref="H9" r:id="rId9" display="ankit@quadlabs.com" xr:uid="{2B2EEA1F-61B1-46BB-90EB-601971FEFFFC}"/>
+    <hyperlink ref="G5" r:id="rId10" display="EE6B4B@E7" xr:uid="{AA01BE6A-C0E4-4436-AC7A-E219DE882D4B}"/>
+    <hyperlink ref="G3" r:id="rId11" display="EE6B4B@E7" xr:uid="{E1915A7C-7027-4800-911E-0273F0422994}"/>
+    <hyperlink ref="G6" r:id="rId12" display="EE6B4B@E7" xr:uid="{6A4F5987-D53D-4D99-8AB2-4B99F25DAE40}"/>
+    <hyperlink ref="G4" r:id="rId13" display="EE6B4B@E7" xr:uid="{D0BC91BE-D830-47D1-B6D5-88BF8FA3B08F}"/>
+    <hyperlink ref="G7" r:id="rId14" display="EE6B4B@E7" xr:uid="{180BDEB3-4CAF-406F-B24D-2D43C5A60610}"/>
+    <hyperlink ref="G8" r:id="rId15" display="EE6B4B@E7" xr:uid="{A0D592EC-45E5-4E0E-BED9-634D2D63FD76}"/>
+    <hyperlink ref="G9" r:id="rId16" display="EE6B4B@E7" xr:uid="{C9523CD0-1DBE-42BE-8121-EAEA1A6C6988}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD7348B-1C26-4C3D-9CF5-A0BF72E36012}">
+  <dimension ref="A1:BP2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="BC1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="BD1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="BE1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="BG1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="BH1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="BI1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BJ1" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="BK1" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL1" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="BO1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BP1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="9">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="M2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>201</v>
+      </c>
+      <c r="S2" t="s">
+        <v>219</v>
+      </c>
+      <c r="T2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2">
+        <v>1320</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z2">
+        <v>6</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB2">
+        <v>14</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE2">
+        <v>784559</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI2">
+        <v>143</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK2">
+        <v>14</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM2">
+        <v>16</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP2">
+        <v>784525</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR2">
+        <v>50</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX2">
+        <v>60</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA2">
+        <v>2</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>30</v>
+      </c>
+      <c r="BD2">
+        <v>70</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>182</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BG2">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>182</v>
+      </c>
+      <c r="BK2" s="9">
+        <v>3</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN2">
+        <v>30</v>
+      </c>
+      <c r="BO2" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{7B346A0F-6A14-44CE-9236-30656838FFF3}">
+      <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{117E0D9B-85E4-4BB8-8BD4-1EC25B69C588}">
+      <formula1>"E0@DA44FE,Ankur@721,Piyush@12345"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{472DC225-5A59-472F-801C-90D03EE59314}">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2" xr:uid="{D5C2FD37-7AAE-43D2-886C-313E7A2CC788}">
+      <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ2 BE2 AY2 AS2" xr:uid="{F0382529-793A-48FF-AA13-426E12998336}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2 BA2" xr:uid="{68223B98-BA59-4AEC-BFD6-877DA53F7C29}">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP2" xr:uid="{797C8C9F-FB56-4136-A047-7D32A6AE7632}">
+      <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2" xr:uid="{AF6642C1-C395-49ED-AA0C-24928D50F6E6}">
+      <formula1>"One Way,Round Trip"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2" xr:uid="{3EEAAD25-A142-4902-834E-3A2315B1474C}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{AD2B7490-CED1-4A84-98F9-FA72259A9122}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{911D7F0E-E042-436E-B6FA-3513A65C93C9}">
+      <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{EC8525B9-7061-46B9-9C12-8C9BD073E7C6}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2" xr:uid="{BE8089B9-23B0-4254-A27F-408604CB9FBA}">
+      <formula1>"1,2,0"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{CAA6CDCE-51B9-485D-B6AF-E35A0B8D3A5B}"/>
+    <hyperlink ref="G2" r:id="rId2" display="EE6B4B@E7" xr:uid="{486C8D13-154B-4139-8F8E-5C8D56581D30}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6636F4-599F-43D1-9219-436D88D19FD0}">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
@@ -3788,260 +6334,53 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="I7" s="15">
-        <v>1</v>
-      </c>
-      <c r="J7" s="15">
-        <v>1</v>
-      </c>
-      <c r="K7" s="15">
-        <v>1</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="S7" s="3">
-        <v>124579</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X7" s="3">
-        <v>123</v>
-      </c>
-      <c r="Y7" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>12</v>
-      </c>
-      <c r="AA7" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>14</v>
-      </c>
-      <c r="AC7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>784522</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI7" s="3">
-        <v>128</v>
-      </c>
-      <c r="AJ7" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="AK7" s="3">
-        <v>12</v>
-      </c>
-      <c r="AL7" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="AM7" s="3">
-        <v>14</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AP7" s="3">
-        <v>784542</v>
-      </c>
-      <c r="AQ7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR7" s="3">
-        <v>100</v>
-      </c>
-      <c r="AS7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AT7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AU7" s="3">
-        <v>2</v>
-      </c>
-      <c r="AV7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AW7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AX7" s="3">
-        <v>100</v>
-      </c>
-      <c r="AY7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AZ7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="BA7" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="BC7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="BD7" s="3">
-        <v>100</v>
-      </c>
-      <c r="BE7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="BF7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="BG7" s="3">
-        <v>2</v>
-      </c>
-      <c r="BH7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="BI7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="BJ7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="BK7" s="15">
-        <v>2</v>
-      </c>
-      <c r="BL7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="BM7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BN7" s="3">
-        <v>30</v>
-      </c>
-      <c r="BO7" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="BP7" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2 H7" xr:uid="{4403D22A-996F-42F6-8666-7148C2838701}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{4403D22A-996F-42F6-8666-7148C2838701}">
       <formula1>"kumar.gaurav@quadlabs.com,ankit@quadlabs.com,akshay.kumar@quadlabs.com"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2 E7" xr:uid="{578BBCD2-A84E-4647-965C-511B261B370C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{578BBCD2-A84E-4647-965C-511B261B370C}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2 BK7" xr:uid="{13357FA9-8F0C-491A-B85B-8B37C8353FBB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2" xr:uid="{13357FA9-8F0C-491A-B85B-8B37C8353FBB}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 V7" xr:uid="{FBAA2943-1C80-452C-BA32-4664FA48724E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2" xr:uid="{FBAA2943-1C80-452C-BA32-4664FA48724E}">
       <formula1>"One Way,Round Trip"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP2 BP7" xr:uid="{A5C3FAC0-3434-4CDE-9837-4EE2CD43343D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP2" xr:uid="{A5C3FAC0-3434-4CDE-9837-4EE2CD43343D}">
       <formula1>"Adjustment,Bank Draft,Inter Booking Transfer,Net Banking,Credit Card,Bank Transfer,Debit Card,Cash,Cheque,Direct Deposit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2 BG2 BA2 AU7 BG7 BA7" xr:uid="{7863FD1D-1C60-4960-961B-B1042C1B1254}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2 BG2 BA2" xr:uid="{7863FD1D-1C60-4960-961B-B1042C1B1254}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2 BJ2 BE2 AY2 AS7 BJ7 BE7 AY7" xr:uid="{EB7ECBFD-F251-44A6-96DD-11E808A302B5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2 BJ2 BE2 AY2" xr:uid="{EB7ECBFD-F251-44A6-96DD-11E808A302B5}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2 AQ7" xr:uid="{3B47DB0D-E201-4B08-92ED-1AA873834BD3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2" xr:uid="{3B47DB0D-E201-4B08-92ED-1AA873834BD3}">
       <formula1>"ABC Supplier,ATsupplier,BSP Supplier,gaurav travel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2 I7:K7" xr:uid="{4AF6D9F2-D7C7-4553-924C-B50ADA76F216}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:K2" xr:uid="{4AF6D9F2-D7C7-4553-924C-B50ADA76F216}">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2 G7" xr:uid="{64582CA8-9D40-496A-A231-B75BCC1C5A4A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{64582CA8-9D40-496A-A231-B75BCC1C5A4A}">
       <formula1>"EE6B4B@E7,Ankur@12345,F1CD@9E4B"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2 F7" xr:uid="{F082A59C-18BF-437E-8467-B3D9A3F2AA8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{F082A59C-18BF-437E-8467-B3D9A3F2AA8E}">
       <formula1>"Piyush_ql,ankur_ql"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2 D7" xr:uid="{82D07BE0-A266-4170-A831-23DCCF6CCE50}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{82D07BE0-A266-4170-A831-23DCCF6CCE50}">
       <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{A8A95E21-E296-4614-AB19-754374DC26B7}"/>
-    <hyperlink ref="H7" r:id="rId2" display="ankit@quadlabs.com" xr:uid="{8A55756D-3228-4307-8406-E15AD9F86C2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B11FD07-B25D-40B3-9560-6C442FC09448}">
   <dimension ref="A1:BP3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4275,7 +6614,7 @@
         <v>171</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>160</v>
@@ -4455,7 +6794,7 @@
         <v>30</v>
       </c>
       <c r="BO2" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="BP2" t="s">
         <v>34</v>
@@ -4466,7 +6805,7 @@
         <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -4499,7 +6838,7 @@
         <v>172</v>
       </c>
       <c r="M3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N3" t="s">
         <v>71</v>
@@ -4541,7 +6880,7 @@
         <v>12</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AB3">
         <v>14</v>
@@ -4661,7 +7000,7 @@
         <v>30</v>
       </c>
       <c r="BO3" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="BP3" t="s">
         <v>34</v>
@@ -4713,13 +7052,13 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="ankit@quadlabs.com" xr:uid="{E0855438-FAC1-4790-AE9C-0A10C4C1EC62}"/>
     <hyperlink ref="H3" r:id="rId2" display="ankit@quadlabs.com" xr:uid="{A95AA7B7-E0CB-4C67-A2FC-3BCF527C0400}"/>
-    <hyperlink ref="G2" r:id="rId3" xr:uid="{04D498EC-AC45-40FC-A898-70AB274FCC11}"/>
+    <hyperlink ref="G2" r:id="rId3" display="EE6B4B@E7" xr:uid="{04D498EC-AC45-40FC-A898-70AB274FCC11}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58C3E7EC-15CC-441E-B49C-BA8A79140B5B}">
   <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6714,7 +9053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E601FE76-DA4B-4D2F-B892-1691EE89E2D6}">
   <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6941,11 +9280,11 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>175</v>
+      <c r="F2" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>162</v>
@@ -6984,10 +9323,10 @@
         <v>124578</v>
       </c>
       <c r="T2" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="U2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="V2" t="s">
         <v>36</v>
@@ -7017,7 +9356,7 @@
         <v>22</v>
       </c>
       <c r="AE2">
-        <v>784521</v>
+        <v>784539</v>
       </c>
       <c r="AF2" t="s">
         <v>14</v>
@@ -7035,7 +9374,7 @@
         <v>167</v>
       </c>
       <c r="AK2" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AL2" s="12" t="s">
         <v>168</v>
@@ -7050,7 +9389,7 @@
         <v>22</v>
       </c>
       <c r="AP2">
-        <v>784541</v>
+        <v>784549</v>
       </c>
       <c r="AQ2" t="s">
         <v>24</v>
@@ -7110,7 +9449,7 @@
         <v>30</v>
       </c>
       <c r="BJ2" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="BK2" s="9">
         <v>3</v>
@@ -7122,10 +9461,10 @@
         <v>115</v>
       </c>
       <c r="BN2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BO2" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="BP2" t="s">
         <v>34</v>
@@ -7154,19 +9493,22 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2" xr:uid="{C0707CF0-FB44-4D09-A9A3-97C93F5169D6}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{3886261B-195F-42BC-B7B5-C7CAE702F4FA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{7D6746F4-2E24-423B-A630-957C4EADE5C4}">
       <formula1>"//xchangev12/backoffice/Home.aspx, //v12staging/backoffice/"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{B27E87B7-76AF-44F1-B8E1-BA43A97E1041}">
-      <formula1>"Piyush_ql,ankur_ql"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{C5E9C7AF-336C-4D66-9D15-5D639DEBA523}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{E4978782-4E59-4E0A-A892-AC3768536D38}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{AA08BD85-18CA-4630-9F60-5E2AE88CB0D2}">
-      <formula1>"EE6B4B@E7,Ankur@12345,F1CD@9E4B"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{79ACFDE6-1A29-4986-B605-94CF24BB792E}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{1C779AA1-7E74-450C-BEEF-776A30A6BB1C}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="EE6B4B@E7" xr:uid="{221E3EC7-C99B-4082-A314-F6818736148F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>